--- a/_ForDRA/BVSimulationFiles/89.xlsx
+++ b/_ForDRA/BVSimulationFiles/89.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0001457627118644068</v>
+        <v>0.002915254237288136</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001693131132917038</v>
+        <v>0.003386262265834076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001928635147190009</v>
+        <v>0.003857270294380018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0002164139161462979</v>
+        <v>0.004328278322925958</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000239964317573595</v>
+        <v>0.0047992863514719</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000263514719000892</v>
+        <v>0.00527029438001784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000287065120428189</v>
+        <v>0.00574130240856378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003106155218554861</v>
+        <v>0.006212310437109722</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0003341659232827832</v>
+        <v>0.006683318465655664</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003577163247100803</v>
+        <v>0.007154326494201606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003812667261373773</v>
+        <v>0.007625334522747546</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004048171275646743</v>
+        <v>0.008096342551293486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004283675289919714</v>
+        <v>0.008567350579839428</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004519179304192685</v>
+        <v>0.00903835860838537</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004754683318465655</v>
+        <v>0.00950936663693131</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0004990187332738625</v>
+        <v>0.00998037466547725</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005225691347011596</v>
+        <v>0.01045138269402319</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005461195361284567</v>
+        <v>0.01092239072256913</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005696699375557537</v>
+        <v>0.01139339875111507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005932203389830508</v>
+        <v>0.01186440677966102</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001457627118644068</v>
+        <v>0.002915254237288136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001693131132917038</v>
+        <v>0.003386262265834076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001928635147190009</v>
+        <v>0.003857270294380018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002164139161462979</v>
+        <v>0.004328278322925958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000239964317573595</v>
+        <v>0.0047992863514719</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000263514719000892</v>
+        <v>0.00527029438001784</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000287065120428189</v>
+        <v>0.00574130240856378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003106155218554861</v>
+        <v>0.006212310437109722</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0003341659232827832</v>
+        <v>0.006683318465655664</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003577163247100803</v>
+        <v>0.007154326494201606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003812667261373773</v>
+        <v>0.007625334522747546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004048171275646743</v>
+        <v>0.008096342551293486</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004283675289919714</v>
+        <v>0.008567350579839428</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004519179304192685</v>
+        <v>0.00903835860838537</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004754683318465655</v>
+        <v>0.00950936663693131</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004990187332738625</v>
+        <v>0.00998037466547725</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005225691347011596</v>
+        <v>0.01045138269402319</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005461195361284567</v>
+        <v>0.01092239072256913</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005696699375557537</v>
+        <v>0.01139339875111507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005932203389830508</v>
+        <v>0.01186440677966102</v>
       </c>
     </row>
   </sheetData>
